--- a/main/ig/ValueSet-jdv-ror-specialite-ordinale.xlsx
+++ b/main/ig/ValueSet-jdv-ror-specialite-ordinale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T08:27:13+00:00</t>
+    <t>2026-08-19T08:37:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-jdv-ror-specialite-ordinale.xlsx
+++ b/main/ig/ValueSet-jdv-ror-specialite-ordinale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T08:37:25+00:00</t>
+    <t>2026-09-15T16:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
